--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0003_ses-01_pet_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0003_ses-01_pet_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -192,7 +193,7 @@
         <v>0.01639209900827801</v>
       </c>
       <c r="E1" s="0">
-        <v>0.024919789427779337</v>
+        <v>0.024919789427779338</v>
       </c>
       <c r="F1" s="0">
         <v>0.011477432498350119</v>
@@ -444,7 +445,7 @@
         <v>0.010541851149061776</v>
       </c>
       <c r="CK1" s="0">
-        <v>0.05108556832694764</v>
+        <v>0.051085568326947641</v>
       </c>
       <c r="CL1" s="0">
         <v>0.031577617784514338</v>
@@ -719,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="BH2" s="0">
-        <v>0.022311468094600623</v>
+        <v>0.022311468094600624</v>
       </c>
       <c r="BI2" s="0">
         <v>0.010758472296933835</v>
@@ -1081,7 +1082,7 @@
         <v>0.012322858903265557</v>
       </c>
       <c r="BH3" s="0">
-        <v>0.022311468094600623</v>
+        <v>0.022311468094600624</v>
       </c>
       <c r="BI3" s="0">
         <v>0.02151694459386767</v>
@@ -1631,7 +1632,7 @@
         <v>0.012075836251660428</v>
       </c>
       <c r="B5" s="0">
-        <v>0.058538217093159393</v>
+        <v>0.058538217093159394</v>
       </c>
       <c r="C5" s="0">
         <v>0.020621593754603033</v>
@@ -1652,7 +1653,7 @@
         <v>0.050459178524573621</v>
       </c>
       <c r="I5" s="0">
-        <v>0.083056478405315617</v>
+        <v>0.083056478405315618</v>
       </c>
       <c r="J5" s="0">
         <v>0.031971353667114268</v>
@@ -1724,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="AG5" s="0">
-        <v>0.037724460540214277</v>
+        <v>0.037724460540214278</v>
       </c>
       <c r="AH5" s="0">
         <v>0.007928956549318111</v>
@@ -1802,7 +1803,7 @@
         <v>0</v>
       </c>
       <c r="BG5" s="0">
-        <v>0.018484288354898334</v>
+        <v>0.018484288354898335</v>
       </c>
       <c r="BH5" s="0">
         <v>0.044622936189201247</v>
@@ -2011,7 +2012,7 @@
         <v>0.066773504273504272</v>
       </c>
       <c r="H6" s="0">
-        <v>0.020183671409829448</v>
+        <v>0.020183671409829449</v>
       </c>
       <c r="I6" s="0">
         <v>0.055370985603543747</v>
@@ -2128,7 +2129,7 @@
         <v>0</v>
       </c>
       <c r="AU6" s="0">
-        <v>0.092729970326409505</v>
+        <v>0.092729970326409506</v>
       </c>
       <c r="AV6" s="0">
         <v>0.014904240256352935</v>
@@ -2173,7 +2174,7 @@
         <v>0.02868925945849023</v>
       </c>
       <c r="BJ6" s="0">
-        <v>0.25428413488114981</v>
+        <v>0.25428413488114982</v>
       </c>
       <c r="BK6" s="0">
         <v>0.054948828903084002</v>
@@ -2245,7 +2246,7 @@
         <v>0.053182059918454178</v>
       </c>
       <c r="CH6" s="0">
-        <v>0.053001192526831858</v>
+        <v>0.053001192526831859</v>
       </c>
       <c r="CI6" s="0">
         <v>0.011092623405435386</v>
@@ -2526,7 +2527,7 @@
         <v>0</v>
       </c>
       <c r="BG7" s="0">
-        <v>0.018484288354898334</v>
+        <v>0.018484288354898335</v>
       </c>
       <c r="BH7" s="0">
         <v>0.083668005354752342</v>
@@ -2861,7 +2862,7 @@
         <v>0.053821313240043064</v>
       </c>
       <c r="AX8" s="0">
-        <v>0.060771801883925856</v>
+        <v>0.060771801883925857</v>
       </c>
       <c r="AY8" s="0">
         <v>0</v>
@@ -3343,7 +3344,7 @@
         <v>0.11068539804171977</v>
       </c>
       <c r="CL9" s="0">
-        <v>0.047366426676771461</v>
+        <v>0.047366426676771462</v>
       </c>
       <c r="CM9" s="0">
         <v>0.018632383081796145</v>
@@ -3462,7 +3463,7 @@
         <v>0.11101019275406207</v>
       </c>
       <c r="I10" s="0">
-        <v>0.18826135105204891</v>
+        <v>0.18826135105204892</v>
       </c>
       <c r="J10" s="0">
         <v>0.10870260246818861</v>
@@ -3528,7 +3529,7 @@
         <v>0.023792529145848226</v>
       </c>
       <c r="AE10" s="0">
-        <v>0.068306010928961824</v>
+        <v>0.068306010928961825</v>
       </c>
       <c r="AF10" s="0">
         <v>0</v>
@@ -3651,7 +3652,7 @@
         <v>0.21810250817884427</v>
       </c>
       <c r="BT10" s="0">
-        <v>0.042398032731281315</v>
+        <v>0.042398032731281316</v>
       </c>
       <c r="BU10" s="0">
         <v>0.010361620557455195</v>
@@ -3941,7 +3942,7 @@
         <v>0.23491592482690382</v>
       </c>
       <c r="AV11" s="0">
-        <v>0.0074521201281764603</v>
+        <v>0.0074521201281764604</v>
       </c>
       <c r="AW11" s="0">
         <v>0.017940437746681002</v>
@@ -3956,7 +3957,7 @@
         <v>0.055576139310855824</v>
       </c>
       <c r="BA11" s="0">
-        <v>0.220195029883611</v>
+        <v>0.22019502988361101</v>
       </c>
       <c r="BB11" s="0">
         <v>0.039424403705893916</v>
@@ -3986,7 +3987,7 @@
         <v>0.61175603464160633</v>
       </c>
       <c r="BK11" s="0">
-        <v>0.068686036128854946</v>
+        <v>0.068686036128854947</v>
       </c>
       <c r="BL11" s="0">
         <v>0.044580308240988367</v>
@@ -4330,7 +4331,7 @@
         <v>0.068516615279205273</v>
       </c>
       <c r="BE12" s="0">
-        <v>0.50007813720893945</v>
+        <v>0.50007813720893946</v>
       </c>
       <c r="BF12" s="0">
         <v>0.041649312786339071</v>
@@ -4339,7 +4340,7 @@
         <v>0.098582871226124552</v>
       </c>
       <c r="BH12" s="0">
-        <v>0.19522534582775566</v>
+        <v>0.19522534582775567</v>
       </c>
       <c r="BI12" s="0">
         <v>0.15061861215707384</v>
@@ -4737,7 +4738,7 @@
         <v>0.36754311563471836</v>
       </c>
       <c r="BT13" s="0">
-        <v>0.12295429492071556</v>
+        <v>0.12295429492071557</v>
       </c>
       <c r="BU13" s="0">
         <v>0</v>
@@ -4958,7 +4959,7 @@
         <v>0.037900322152738336</v>
       </c>
       <c r="Y14" s="0">
-        <v>0.078616352201257927</v>
+        <v>0.078616352201257928</v>
       </c>
       <c r="Z14" s="0">
         <v>0</v>
@@ -5260,7 +5261,7 @@
         <v>0.18304510559243761</v>
       </c>
       <c r="E15" s="0">
-        <v>0.15574868392362073</v>
+        <v>0.15574868392362074</v>
       </c>
       <c r="F15" s="0">
         <v>0.091819459986800869</v>
@@ -5443,7 +5444,7 @@
         <v>0.25493945188017825</v>
       </c>
       <c r="BN15" s="0">
-        <v>0.031046258925799416</v>
+        <v>0.031046258925799417</v>
       </c>
       <c r="BO15" s="0">
         <v>0.11257458065968694</v>
@@ -5452,7 +5453,7 @@
         <v>0.16901822457377996</v>
       </c>
       <c r="BQ15" s="0">
-        <v>0.40679588418281853</v>
+        <v>0.40679588418281854</v>
       </c>
       <c r="BR15" s="0">
         <v>0.16145959473641705</v>
@@ -5509,13 +5510,13 @@
         <v>0</v>
       </c>
       <c r="CJ15" s="0">
-        <v>0.084334809192494128</v>
+        <v>0.084334809192494129</v>
       </c>
       <c r="CK15" s="0">
         <v>0.43138924364977965</v>
       </c>
       <c r="CL15" s="0">
-        <v>0.17683465959328012</v>
+        <v>0.17683465959328013</v>
       </c>
       <c r="CM15" s="0">
         <v>0.074529532327184581</v>
@@ -5646,7 +5647,7 @@
         <v>0.35517670040845356</v>
       </c>
       <c r="M16" s="0">
-        <v>0.37422037422037457</v>
+        <v>0.37422037422037458</v>
       </c>
       <c r="N16" s="0">
         <v>0.10384215991692637</v>
@@ -5733,7 +5734,7 @@
         <v>0.089887640449438283</v>
       </c>
       <c r="AP16" s="0">
-        <v>0.32376747608535716</v>
+        <v>0.32376747608535717</v>
       </c>
       <c r="AQ16" s="0">
         <v>0.32904148783977144</v>
@@ -5769,7 +5770,7 @@
         <v>0.40893362692670693</v>
       </c>
       <c r="BB16" s="0">
-        <v>0.18726591760299643</v>
+        <v>0.18726591760299644</v>
       </c>
       <c r="BC16" s="0">
         <v>0.038090401218892872</v>
@@ -5778,7 +5779,7 @@
         <v>0.21240150736553637</v>
       </c>
       <c r="BE16" s="0">
-        <v>0.84388185654008518</v>
+        <v>0.84388185654008519</v>
       </c>
       <c r="BF16" s="0">
         <v>0.083298625572678142</v>
@@ -5865,7 +5866,7 @@
         <v>0.34863794835431106</v>
       </c>
       <c r="CH16" s="0">
-        <v>0.4151760081268499</v>
+        <v>0.41517600812684991</v>
       </c>
       <c r="CI16" s="0">
         <v>0.033277870216306189</v>
@@ -5975,7 +5976,7 @@
         <v>0.39447731755424026</v>
       </c>
       <c r="B17" s="0">
-        <v>0.53102525505937392</v>
+        <v>0.53102525505937393</v>
       </c>
       <c r="C17" s="0">
         <v>0.39181028133745727</v>
@@ -6098,7 +6099,7 @@
         <v>0.3532008830022072</v>
       </c>
       <c r="AQ17" s="0">
-        <v>0.24320457796852626</v>
+        <v>0.24320457796852627</v>
       </c>
       <c r="AR17" s="0">
         <v>0.13707165109034256</v>
@@ -6110,7 +6111,7 @@
         <v>0.11129660545353358</v>
       </c>
       <c r="AU17" s="0">
-        <v>0.50692383778437144</v>
+        <v>0.50692383778437145</v>
       </c>
       <c r="AV17" s="0">
         <v>0.074521201281764593</v>
@@ -6161,7 +6162,7 @@
         <v>0.28161274812830522</v>
       </c>
       <c r="BL17" s="0">
-        <v>0.18468984842695182</v>
+        <v>0.18468984842695183</v>
       </c>
       <c r="BM17" s="0">
         <v>0.33026247175386725</v>
@@ -6337,7 +6338,7 @@
         <v>0.42667954755866805</v>
       </c>
       <c r="B18" s="0">
-        <v>0.57701956848971347</v>
+        <v>0.57701956848971348</v>
       </c>
       <c r="C18" s="0">
         <v>0.41243187509206036</v>
@@ -6451,7 +6452,7 @@
         <v>0.49428483163422882</v>
       </c>
       <c r="AN18" s="0">
-        <v>0.17383746197305502</v>
+        <v>0.17383746197305503</v>
       </c>
       <c r="AO18" s="0">
         <v>0.31460674157303342</v>
@@ -6529,7 +6530,7 @@
         <v>0.3939973347239118</v>
       </c>
       <c r="BN18" s="0">
-        <v>0.031046258925799416</v>
+        <v>0.031046258925799417</v>
       </c>
       <c r="BO18" s="0">
         <v>0.13508949679162435</v>
@@ -6750,7 +6751,7 @@
         <v>0.68870523415978158</v>
       </c>
       <c r="S19" s="0">
-        <v>0.50617627937215703</v>
+        <v>0.50617627937215704</v>
       </c>
       <c r="T19" s="0">
         <v>0.6351157549682459</v>
@@ -6777,7 +6778,7 @@
         <v>0.35180299032541873</v>
       </c>
       <c r="AB19" s="0">
-        <v>0.30656039239730309</v>
+        <v>0.3065603923973031</v>
       </c>
       <c r="AC19" s="0">
         <v>0.18912529550827478</v>
@@ -6870,10 +6871,10 @@
         <v>0.20824656393169572</v>
       </c>
       <c r="BG19" s="0">
-        <v>0.3080714725816398</v>
+        <v>0.30807147258163981</v>
       </c>
       <c r="BH19" s="0">
-        <v>0.60240963855421858</v>
+        <v>0.60240963855421859</v>
       </c>
       <c r="BI19" s="0">
         <v>0.48771741079433523</v>
@@ -6888,7 +6889,7 @@
         <v>0.26111323398293285</v>
       </c>
       <c r="BM19" s="0">
-        <v>0.45773219769395806</v>
+        <v>0.45773219769395807</v>
       </c>
       <c r="BN19" s="0">
         <v>0.10348752975266509</v>
@@ -6906,7 +6907,7 @@
         <v>0.40364898684104417</v>
       </c>
       <c r="BS19" s="0">
-        <v>0.69873581323963196</v>
+        <v>0.69873581323963197</v>
       </c>
       <c r="BT19" s="0">
         <v>0.49181717968286409</v>
@@ -6924,7 +6925,7 @@
         <v>0.57495442434441324</v>
       </c>
       <c r="BY19" s="0">
-        <v>0.62709030100334628</v>
+        <v>0.62709030100334629</v>
       </c>
       <c r="BZ19" s="0">
         <v>0.35545023696682565</v>
@@ -6954,7 +6955,7 @@
         <v>0.6757652047171081</v>
       </c>
       <c r="CI19" s="0">
-        <v>0.066555740432612503</v>
+        <v>0.066555740432612504</v>
       </c>
       <c r="CJ19" s="0">
         <v>0.14758591608686528</v>
@@ -7082,7 +7083,7 @@
         <v>0.61560197799979766</v>
       </c>
       <c r="I20" s="0">
-        <v>0.68106312292358739</v>
+        <v>0.6810631229235874</v>
       </c>
       <c r="J20" s="0">
         <v>0.69058123920966752</v>
@@ -7175,7 +7176,7 @@
         <v>0.58696323756564672</v>
       </c>
       <c r="AN20" s="0">
-        <v>0.17383746197305502</v>
+        <v>0.17383746197305503</v>
       </c>
       <c r="AO20" s="0">
         <v>0.44943820224719061</v>
@@ -7492,7 +7493,7 @@
         <v>0.30320257722190608</v>
       </c>
       <c r="Y21" s="0">
-        <v>0.44549266247379415</v>
+        <v>0.44549266247379416</v>
       </c>
       <c r="Z21" s="0">
         <v>0.13726835964310216</v>
@@ -7507,7 +7508,7 @@
         <v>0.1654846335697398</v>
       </c>
       <c r="AD21" s="0">
-        <v>0.071377587437544548</v>
+        <v>0.071377587437544549</v>
       </c>
       <c r="AE21" s="0">
         <v>0.3415300546448084</v>
@@ -7522,7 +7523,7 @@
         <v>0.25372660957817927</v>
       </c>
       <c r="AI21" s="0">
-        <v>0.25336981858720969</v>
+        <v>0.2533698185872097</v>
       </c>
       <c r="AJ21" s="0">
         <v>0.65015479876160931</v>
@@ -7537,7 +7538,7 @@
         <v>0.40160642570281091</v>
       </c>
       <c r="AN21" s="0">
-        <v>0.17383746197305502</v>
+        <v>0.17383746197305503</v>
       </c>
       <c r="AO21" s="0">
         <v>0.40449438202247157</v>
@@ -7603,7 +7604,7 @@
         <v>0.58812981889904914</v>
       </c>
       <c r="BJ21" s="0">
-        <v>1.2161415146489762</v>
+        <v>1.2161415146489763</v>
       </c>
       <c r="BK21" s="0">
         <v>0.48767085651487013</v>
@@ -7636,7 +7637,7 @@
         <v>0.69108793351988407</v>
       </c>
       <c r="BU21" s="0">
-        <v>0.15542430836182763</v>
+        <v>0.15542430836182764</v>
       </c>
       <c r="BV21" s="0">
         <v>0.45864045864045822</v>
@@ -7791,7 +7792,7 @@
         <v>0.74532331713065192</v>
       </c>
       <c r="D22" s="0">
-        <v>0.50542305275523824</v>
+        <v>0.50542305275523825</v>
       </c>
       <c r="E22" s="0">
         <v>0.61987976201601047</v>
@@ -8088,13 +8089,13 @@
         <v>0</v>
       </c>
       <c r="CY22" s="0">
-        <v>0.06483507577599476</v>
+        <v>0.064835075775994761</v>
       </c>
       <c r="CZ22" s="0">
         <v>0.077681970014759502</v>
       </c>
       <c r="DA22" s="0">
-        <v>0.60038424591738659</v>
+        <v>0.6003842459173866</v>
       </c>
       <c r="DB22" s="0">
         <v>0</v>
@@ -8153,7 +8154,7 @@
         <v>0.79245838856974737</v>
       </c>
       <c r="D23" s="0">
-        <v>0.52181515176351811</v>
+        <v>0.52181515176351812</v>
       </c>
       <c r="E23" s="0">
         <v>0.69775410397782334</v>
@@ -8420,7 +8421,7 @@
         <v>0.1196458482890647</v>
       </c>
       <c r="CO23" s="0">
-        <v>0.98298510094331581</v>
+        <v>0.98298510094331582</v>
       </c>
       <c r="CP23" s="0">
         <v>0.83942918815205902</v>
@@ -8459,7 +8460,7 @@
         <v>0.93659942363112658</v>
       </c>
       <c r="DB23" s="0">
-        <v>0.026123301985371022</v>
+        <v>0.026123301985371023</v>
       </c>
       <c r="DC23" s="0">
         <v>0.53135758120042054</v>
@@ -8662,7 +8663,7 @@
         <v>0.52488576015808286</v>
       </c>
       <c r="BA24" s="0">
-        <v>1.0066058508965074</v>
+        <v>1.0066058508965075</v>
       </c>
       <c r="BB24" s="0">
         <v>0.48294894539720046</v>
@@ -8824,7 +8825,7 @@
         <v>0.026123301985370925</v>
       </c>
       <c r="DC24" s="0">
-        <v>0.88310133213590702</v>
+        <v>0.88310133213590703</v>
       </c>
       <c r="DD24" s="0">
         <v>0.030358227079538527</v>
@@ -9003,7 +9004,7 @@
         <v>0.13227513227513216</v>
       </c>
       <c r="AT25" s="0">
-        <v>0.44518642181413431</v>
+        <v>0.44518642181413432</v>
       </c>
       <c r="AU25" s="0">
         <v>1.0262116716122642</v>
@@ -9087,7 +9088,7 @@
         <v>0.32121023728111048</v>
       </c>
       <c r="BV25" s="0">
-        <v>0.76986076986076923</v>
+        <v>0.76986076986076924</v>
       </c>
       <c r="BW25" s="0">
         <v>0.3362573099415202</v>
@@ -9135,7 +9136,7 @@
         <v>1.0869873705122737</v>
       </c>
       <c r="CL25" s="0">
-        <v>0.81154477706201777</v>
+        <v>0.81154477706201778</v>
       </c>
       <c r="CM25" s="0">
         <v>0.16769144773616532</v>
@@ -9144,7 +9145,7 @@
         <v>0.28715003589375421</v>
       </c>
       <c r="CO25" s="0">
-        <v>1.115225249052278</v>
+        <v>1.1152252490522781</v>
       </c>
       <c r="CP25" s="0">
         <v>0.98333133469240819</v>
@@ -9216,7 +9217,7 @@
         <v>0.043516100957354184</v>
       </c>
       <c r="DM25" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="DN25" s="0">
         <v>0</v>
@@ -9266,7 +9267,7 @@
         <v>0.78138874089859645</v>
       </c>
       <c r="M26" s="0">
-        <v>1.2889812889812879</v>
+        <v>1.288981288981288</v>
       </c>
       <c r="N26" s="0">
         <v>0.82035306334371683</v>
@@ -9317,7 +9318,7 @@
         <v>0.52009456264775367</v>
       </c>
       <c r="AD26" s="0">
-        <v>0.071377587437544548</v>
+        <v>0.071377587437544549</v>
       </c>
       <c r="AE26" s="0">
         <v>0.75136612021857863</v>
@@ -9353,7 +9354,7 @@
         <v>0.71910112359550493</v>
       </c>
       <c r="AP26" s="0">
-        <v>1.0448859455481962</v>
+        <v>1.0448859455481963</v>
       </c>
       <c r="AQ26" s="0">
         <v>0.90128755364806779</v>
@@ -9449,7 +9450,7 @@
         <v>0.25904051393637939</v>
       </c>
       <c r="BV26" s="0">
-        <v>0.76986076986076923</v>
+        <v>0.76986076986076924</v>
       </c>
       <c r="BW26" s="0">
         <v>0.29239766081871316</v>
@@ -9482,7 +9483,7 @@
         <v>0.63327576280944098</v>
       </c>
       <c r="CG26" s="0">
-        <v>0.94545884299474003</v>
+        <v>0.94545884299474004</v>
       </c>
       <c r="CH26" s="0">
         <v>1.0821076807561494</v>
@@ -9578,7 +9579,7 @@
         <v>0.21758050478677091</v>
       </c>
       <c r="DM26" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="DN26" s="0">
         <v>0</v>
@@ -9587,7 +9588,7 @@
         <v>0.16181229773462769</v>
       </c>
       <c r="DP26" s="0">
-        <v>4.1079812206572734</v>
+        <v>4.1079812206572735</v>
       </c>
     </row>
     <row r="27">
@@ -9622,7 +9623,7 @@
         <v>1.2532770637508781</v>
       </c>
       <c r="K27" s="0">
-        <v>1.0072215887495239</v>
+        <v>1.007221588749524</v>
       </c>
       <c r="L27" s="0">
         <v>0.94121825608240017</v>
@@ -9649,7 +9650,7 @@
         <v>1.1005851212036768</v>
       </c>
       <c r="T27" s="0">
-        <v>1.2702315099364871</v>
+        <v>1.2702315099364872</v>
       </c>
       <c r="U27" s="0">
         <v>0.53913366796802331</v>
@@ -9688,7 +9689,7 @@
         <v>0.42105263157894701</v>
       </c>
       <c r="AG27" s="0">
-        <v>1.1468236004225127</v>
+        <v>1.1468236004225128</v>
       </c>
       <c r="AH27" s="0">
         <v>0.61845861084681197</v>
@@ -9715,7 +9716,7 @@
         <v>0.91385767790262096</v>
       </c>
       <c r="AP27" s="0">
-        <v>0.88300220750551794</v>
+        <v>0.88300220750551795</v>
       </c>
       <c r="AQ27" s="0">
         <v>0.90128755364806779</v>
@@ -9739,7 +9740,7 @@
         <v>0.9598134194474337</v>
       </c>
       <c r="AX27" s="0">
-        <v>0.76977615719639358</v>
+        <v>0.76977615719639359</v>
       </c>
       <c r="AY27" s="0">
         <v>0.44489383215369022</v>
@@ -9772,7 +9773,7 @@
         <v>1.176929941990182</v>
       </c>
       <c r="BI27" s="0">
-        <v>0.96109019185942179</v>
+        <v>0.9610901918594218</v>
       </c>
       <c r="BJ27" s="0">
         <v>1.2972176156255746</v>
@@ -9784,7 +9785,7 @@
         <v>0.90434339574576406</v>
       </c>
       <c r="BM27" s="0">
-        <v>1.1182571412016908</v>
+        <v>1.1182571412016909</v>
       </c>
       <c r="BN27" s="0">
         <v>0.20697505950532943</v>
@@ -9835,7 +9836,7 @@
         <v>1.149856267966503</v>
       </c>
       <c r="CD27" s="0">
-        <v>0.64102564102564052</v>
+        <v>0.64102564102564053</v>
       </c>
       <c r="CE27" s="0">
         <v>1.0158730158730149</v>
@@ -10074,7 +10075,7 @@
         <v>0.39113428943937528</v>
       </c>
       <c r="AO28" s="0">
-        <v>0.77902621722846654</v>
+        <v>0.77902621722846655</v>
       </c>
       <c r="AP28" s="0">
         <v>1.2509197939661549</v>
@@ -10089,7 +10090,7 @@
         <v>0.19841269841269896</v>
       </c>
       <c r="AT28" s="0">
-        <v>0.44518642181413592</v>
+        <v>0.44518642181413593</v>
       </c>
       <c r="AU28" s="0">
         <v>1.3600395647873431</v>
@@ -10230,7 +10231,7 @@
         <v>0.38286671452500709</v>
       </c>
       <c r="CO28" s="0">
-        <v>1.2122013576655239</v>
+        <v>1.212201357665524</v>
       </c>
       <c r="CP28" s="0">
         <v>1.2591437822280884</v>
@@ -10302,7 +10303,7 @@
         <v>0.60922541340296088</v>
       </c>
       <c r="DM28" s="0">
-        <v>3.7749287749287856</v>
+        <v>3.7749287749287857</v>
       </c>
       <c r="DN28" s="0">
         <v>0.1302083333333337</v>
@@ -10325,7 +10326,7 @@
         <v>1.1901605538370883</v>
       </c>
       <c r="D29" s="0">
-        <v>0.95074174248012377</v>
+        <v>0.95074174248012378</v>
       </c>
       <c r="E29" s="0">
         <v>1.1899199451764622</v>
@@ -10349,7 +10350,7 @@
         <v>1.501330292664385</v>
       </c>
       <c r="L29" s="0">
-        <v>1.1188066062866266</v>
+        <v>1.1188066062866267</v>
       </c>
       <c r="M29" s="0">
         <v>1.4275814275814265</v>
@@ -10373,7 +10374,7 @@
         <v>1.1981053218166609</v>
       </c>
       <c r="T29" s="0">
-        <v>1.3453527282660644</v>
+        <v>1.3453527282660645</v>
       </c>
       <c r="U29" s="0">
         <v>0.7994050938836208</v>
@@ -10412,7 +10413,7 @@
         <v>0.77192982456140291</v>
       </c>
       <c r="AG29" s="0">
-        <v>1.1468236004225127</v>
+        <v>1.1468236004225128</v>
       </c>
       <c r="AH29" s="0">
         <v>0.64224548049476626</v>
@@ -10466,7 +10467,7 @@
         <v>0.9419629292008499</v>
       </c>
       <c r="AY29" s="0">
-        <v>0.5325244354566897</v>
+        <v>0.53252443545668971</v>
       </c>
       <c r="AZ29" s="0">
         <v>0.96331974805483422</v>
@@ -10583,7 +10584,7 @@
         <v>1.3339009507591872</v>
       </c>
       <c r="CL29" s="0">
-        <v>0.92838196286472074</v>
+        <v>0.92838196286472075</v>
       </c>
       <c r="CM29" s="0">
         <v>0.6148686416992728</v>
@@ -10595,7 +10596,7 @@
         <v>1.366481530459313</v>
       </c>
       <c r="CP29" s="0">
-        <v>1.1472198904744761</v>
+        <v>1.1472198904744762</v>
       </c>
       <c r="CQ29" s="0">
         <v>0.097529258777633215</v>
@@ -10616,13 +10617,13 @@
         <v>1.6169154228855707</v>
       </c>
       <c r="CW29" s="0">
-        <v>0.48537798810823884</v>
+        <v>0.48537798810823885</v>
       </c>
       <c r="CX29" s="0">
         <v>0.57526366251198413</v>
       </c>
       <c r="CY29" s="0">
-        <v>2.3016451900478136</v>
+        <v>2.3016451900478137</v>
       </c>
       <c r="CZ29" s="0">
         <v>2.5790414044900154</v>
@@ -10637,7 +10638,7 @@
         <v>3.7344708875916743</v>
       </c>
       <c r="DD29" s="0">
-        <v>0.98360655737704838</v>
+        <v>0.98360655737704839</v>
       </c>
       <c r="DE29" s="0">
         <v>1.5305300467214422</v>
@@ -10649,7 +10650,7 @@
         <v>0</v>
       </c>
       <c r="DH29" s="0">
-        <v>1.158645276292334</v>
+        <v>1.1586452762923341</v>
       </c>
       <c r="DI29" s="0">
         <v>2.8037383177570065</v>
@@ -10681,7 +10682,7 @@
         <v>1.3202914301815387</v>
       </c>
       <c r="B30" s="0">
-        <v>1.2669342699448058</v>
+        <v>1.2669342699448059</v>
       </c>
       <c r="C30" s="0">
         <v>1.2019443216968615</v>
@@ -10714,13 +10715,13 @@
         <v>1.3141537915112758</v>
       </c>
       <c r="M30" s="0">
-        <v>1.2889812889812879</v>
+        <v>1.288981288981288</v>
       </c>
       <c r="N30" s="0">
         <v>0.84112149532710212</v>
       </c>
       <c r="O30" s="0">
-        <v>1.2392063805945543</v>
+        <v>1.2392063805945544</v>
       </c>
       <c r="P30" s="0">
         <v>1.3820167206961256</v>
@@ -10729,7 +10730,7 @@
         <v>1.4917695473251014</v>
       </c>
       <c r="R30" s="0">
-        <v>1.5610651974288325</v>
+        <v>1.5610651974288326</v>
       </c>
       <c r="S30" s="0">
         <v>1.2677626079687923</v>
@@ -10780,7 +10781,7 @@
         <v>0.70567713288931111</v>
       </c>
       <c r="AI30" s="0">
-        <v>0.90199655417046642</v>
+        <v>0.90199655417046643</v>
       </c>
       <c r="AJ30" s="0">
         <v>1.3622291021671813</v>
@@ -10855,7 +10856,7 @@
         <v>1.0289587184226732</v>
       </c>
       <c r="BH30" s="0">
-        <v>1.2717536813922345</v>
+        <v>1.2717536813922346</v>
       </c>
       <c r="BI30" s="0">
         <v>1.2479827864443238</v>
@@ -10912,7 +10913,7 @@
         <v>0.85571353343865109</v>
       </c>
       <c r="CA30" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB30" s="0">
         <v>1.1023622047244084</v>
@@ -10924,7 +10925,7 @@
         <v>0.65384615384615319</v>
       </c>
       <c r="CE30" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="CF30" s="0">
         <v>0.6908462867012084</v>
@@ -10942,7 +10943,7 @@
         <v>0.68522032468901484</v>
       </c>
       <c r="CK30" s="0">
-        <v>1.2374059883638417</v>
+        <v>1.2374059883638418</v>
       </c>
       <c r="CL30" s="0">
         <v>1.1525830491347722</v>
@@ -11029,7 +11030,7 @@
         <v>3.4188034188034155</v>
       </c>
       <c r="DN30" s="0">
-        <v>0.58593749999999944</v>
+        <v>0.58593749999999945</v>
       </c>
       <c r="DO30" s="0">
         <v>1.4563106796116492</v>
@@ -11178,13 +11179,13 @@
         <v>0.83472454090150183</v>
       </c>
       <c r="AU31" s="0">
-        <v>1.2796735905044498</v>
+        <v>1.2796735905044499</v>
       </c>
       <c r="AV31" s="0">
         <v>0.6408823310231756</v>
       </c>
       <c r="AW31" s="0">
-        <v>1.1930391101542865</v>
+        <v>1.1930391101542866</v>
       </c>
       <c r="AX31" s="0">
         <v>1.245821938620479</v>
@@ -11214,7 +11215,7 @@
         <v>0.99958350687213571</v>
       </c>
       <c r="BG31" s="0">
-        <v>1.0720887245841026</v>
+        <v>1.0720887245841027</v>
       </c>
       <c r="BH31" s="0">
         <v>1.221552878179383</v>
@@ -11232,7 +11233,7 @@
         <v>0.99350401222774076</v>
       </c>
       <c r="BM31" s="0">
-        <v>1.1588156903644466</v>
+        <v>1.1588156903644467</v>
       </c>
       <c r="BN31" s="0">
         <v>0.34150884818379351</v>
@@ -11423,10 +11424,10 @@
         <v>1.4423076923076963</v>
       </c>
       <c r="H32" s="0">
-        <v>1.3523059844585767</v>
+        <v>1.3523059844585768</v>
       </c>
       <c r="I32" s="0">
-        <v>1.1960132890365482</v>
+        <v>1.1960132890365483</v>
       </c>
       <c r="J32" s="0">
         <v>1.3619796662190715</v>
@@ -11495,7 +11496,7 @@
         <v>1.297814207650277</v>
       </c>
       <c r="AF32" s="0">
-        <v>0.6315789473684229</v>
+        <v>0.63157894736842291</v>
       </c>
       <c r="AG32" s="0">
         <v>1.2524520899351175</v>
@@ -11567,7 +11568,7 @@
         <v>0.7702725579820574</v>
       </c>
       <c r="BD32" s="0">
-        <v>1.1579307982185711</v>
+        <v>1.1579307982185712</v>
       </c>
       <c r="BE32" s="0">
         <v>1.2658227848101302</v>
@@ -11600,7 +11601,7 @@
         <v>0.70371520231812268</v>
       </c>
       <c r="BO32" s="0">
-        <v>0.91185410334346761</v>
+        <v>0.91185410334346762</v>
       </c>
       <c r="BP32" s="0">
         <v>1.3080540858318672</v>
@@ -11696,7 +11697,7 @@
         <v>1.7220664797757357</v>
       </c>
       <c r="CU32" s="0">
-        <v>2.7944111776447182</v>
+        <v>2.7944111776447183</v>
       </c>
       <c r="CV32" s="0">
         <v>3.6691542288557315</v>
@@ -11791,7 +11792,7 @@
         <v>1.3178294573643399</v>
       </c>
       <c r="J33" s="0">
-        <v>1.1957286271500724</v>
+        <v>1.1957286271500725</v>
       </c>
       <c r="K33" s="0">
         <v>1.4823261117445825</v>
@@ -11803,7 +11804,7 @@
         <v>0.99792099792099709</v>
       </c>
       <c r="N33" s="0">
-        <v>1.3084112149532698</v>
+        <v>1.3084112149532699</v>
       </c>
       <c r="O33" s="0">
         <v>1.1996572407883452</v>
@@ -11890,7 +11891,7 @@
         <v>1.2509197939661503</v>
       </c>
       <c r="AQ33" s="0">
-        <v>1.373390557939913</v>
+        <v>1.3733905579399131</v>
       </c>
       <c r="AR33" s="0">
         <v>0.98442367601246017</v>
@@ -11920,7 +11921,7 @@
         <v>1.142398419167592</v>
       </c>
       <c r="BA33" s="0">
-        <v>1.1743734927125919</v>
+        <v>1.174373492712592</v>
       </c>
       <c r="BB33" s="0">
         <v>1.2911492213680258</v>
@@ -12085,7 +12086,7 @@
         <v>2.6942074539739536</v>
       </c>
       <c r="DD33" s="0">
-        <v>3.5094110503946538</v>
+        <v>3.5094110503946539</v>
       </c>
       <c r="DE33" s="0">
         <v>3.8504913806992072</v>
@@ -12213,7 +12214,7 @@
         <v>1.2056737588652471</v>
       </c>
       <c r="AD34" s="0">
-        <v>0.54722817035450821</v>
+        <v>0.54722817035450822</v>
       </c>
       <c r="AE34" s="0">
         <v>1.092896174863387</v>
@@ -12237,7 +12238,7 @@
         <v>1.2554787905801936</v>
       </c>
       <c r="AL34" s="0">
-        <v>1.2832914167795177</v>
+        <v>1.2832914167795178</v>
       </c>
       <c r="AM34" s="0">
         <v>1.3901760889712684</v>
@@ -12270,7 +12271,7 @@
         <v>1.006036217303822</v>
       </c>
       <c r="AW34" s="0">
-        <v>1.4172945819877993</v>
+        <v>1.4172945819877994</v>
       </c>
       <c r="AX34" s="0">
         <v>1.2762078395624419</v>
@@ -12285,7 +12286,7 @@
         <v>1.3106847016881606</v>
       </c>
       <c r="BB34" s="0">
-        <v>1.1038833037650297</v>
+        <v>1.1038833037650298</v>
       </c>
       <c r="BC34" s="0">
         <v>0.93956323006602249</v>
@@ -12318,7 +12319,7 @@
         <v>1.108139090561711</v>
       </c>
       <c r="BM34" s="0">
-        <v>1.4195492206964468</v>
+        <v>1.4195492206964469</v>
       </c>
       <c r="BN34" s="0">
         <v>0.84859774397185062</v>
@@ -12363,7 +12364,7 @@
         <v>1.1528822055137835</v>
       </c>
       <c r="CB34" s="0">
-        <v>1.5223097112860879</v>
+        <v>1.522309711286088</v>
       </c>
       <c r="CC34" s="0">
         <v>1.1373578302712151</v>
@@ -12393,7 +12394,7 @@
         <v>1.1919965942954438</v>
       </c>
       <c r="CL34" s="0">
-        <v>1.2473159024883151</v>
+        <v>1.2473159024883152</v>
       </c>
       <c r="CM34" s="0">
         <v>0.98751630333519569</v>
@@ -12533,7 +12534,7 @@
         <v>1.1666996242831709</v>
       </c>
       <c r="P35" s="0">
-        <v>1.1886481260308241</v>
+        <v>1.1886481260308242</v>
       </c>
       <c r="Q35" s="0">
         <v>1.3374485596707806</v>
@@ -12554,7 +12555,7 @@
         <v>0.93443627450980316</v>
       </c>
       <c r="W35" s="0">
-        <v>0.66666666666666607</v>
+        <v>0.66666666666666608</v>
       </c>
       <c r="X35" s="0">
         <v>1.0801591813530407</v>
@@ -12644,7 +12645,7 @@
         <v>1.2412004446091134</v>
       </c>
       <c r="BA35" s="0">
-        <v>1.1429170598720761</v>
+        <v>1.1429170598720762</v>
       </c>
       <c r="BB35" s="0">
         <v>1.1925882121032907</v>
@@ -12653,7 +12654,7 @@
         <v>0.99035043169121295</v>
       </c>
       <c r="BD35" s="0">
-        <v>1.3155190133607388</v>
+        <v>1.3155190133607389</v>
       </c>
       <c r="BE35" s="0">
         <v>1.0157837162056562</v>
@@ -12827,7 +12828,7 @@
         <v>2.8037383177570065</v>
       </c>
       <c r="DJ35" s="0">
-        <v>1.7615176151761502</v>
+        <v>1.7615176151761503</v>
       </c>
       <c r="DK35" s="0">
         <v>3.3518261673601448</v>
@@ -13102,7 +13103,7 @@
         <v>1.0938399539435799</v>
       </c>
       <c r="CG36" s="0">
-        <v>1.2172782603557279</v>
+        <v>1.217278260355728</v>
       </c>
       <c r="CH36" s="0">
         <v>1.1483591714146892</v>
@@ -13138,7 +13139,7 @@
         <v>3.8244380526259687</v>
       </c>
       <c r="CS36" s="0">
-        <v>3.9141972578505055</v>
+        <v>3.9141972578505056</v>
       </c>
       <c r="CT36" s="0">
         <v>0.13349352556401003</v>
@@ -13239,7 +13240,7 @@
         <v>1.1129568106312282</v>
       </c>
       <c r="J37" s="0">
-        <v>1.0998145661487297</v>
+        <v>1.0998145661487298</v>
       </c>
       <c r="K37" s="0">
         <v>1.1212466742683382</v>
@@ -13311,7 +13312,7 @@
         <v>1.154368492530556</v>
       </c>
       <c r="AH37" s="0">
-        <v>1.2607040913415783</v>
+        <v>1.2607040913415784</v>
       </c>
       <c r="AI37" s="0">
         <v>1.2972534711665136</v>
@@ -13332,7 +13333,7 @@
         <v>1.2168622338113853</v>
       </c>
       <c r="AO37" s="0">
-        <v>1.4232209737827703</v>
+        <v>1.4232209737827704</v>
       </c>
       <c r="AP37" s="0">
         <v>1.1037527593818977</v>
@@ -13407,7 +13408,7 @@
         <v>1.1124630627498686</v>
       </c>
       <c r="BN37" s="0">
-        <v>1.1073165683535124</v>
+        <v>1.1073165683535125</v>
       </c>
       <c r="BO37" s="0">
         <v>1.1707756388607442</v>
@@ -13455,7 +13456,7 @@
         <v>0.86239220097487745</v>
       </c>
       <c r="CD37" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="CE37" s="0">
         <v>0.95238095238095155</v>
@@ -13566,7 +13567,7 @@
         <v>3.971354166666663</v>
       </c>
       <c r="DO37" s="0">
-        <v>2.9126213592232983</v>
+        <v>2.9126213592232984</v>
       </c>
       <c r="DP37" s="0">
         <v>0</v>
@@ -13640,10 +13641,10 @@
         <v>1.2408088235294199</v>
       </c>
       <c r="W38" s="0">
-        <v>0.5811965811965849</v>
+        <v>0.58119658119658491</v>
       </c>
       <c r="X38" s="0">
-        <v>1.4212620807276954</v>
+        <v>1.4212620807276955</v>
       </c>
       <c r="Y38" s="0">
         <v>1.3888888888888979</v>
@@ -13682,7 +13683,7 @@
         <v>0.94943240454076983</v>
       </c>
       <c r="AK38" s="0">
-        <v>1.1811901047470545</v>
+        <v>1.1811901047470546</v>
       </c>
       <c r="AL38" s="0">
         <v>1.2639453150190318</v>
@@ -13969,10 +13970,10 @@
         <v>0.96921322690991929</v>
       </c>
       <c r="L39" s="0">
-        <v>1.1188066062866266</v>
+        <v>1.1188066062866267</v>
       </c>
       <c r="M39" s="0">
-        <v>0.91476091476091403</v>
+        <v>0.91476091476091404</v>
       </c>
       <c r="N39" s="0">
         <v>1.1318795430944955</v>
@@ -14101,7 +14102,7 @@
         <v>1.180802437785677</v>
       </c>
       <c r="BD39" s="0">
-        <v>1.2949640287769772</v>
+        <v>1.2949640287769773</v>
       </c>
       <c r="BE39" s="0">
         <v>0.60947022972339371</v>
@@ -14179,7 +14180,7 @@
         <v>0.73740782402199667</v>
       </c>
       <c r="CD39" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="CE39" s="0">
         <v>1.4603174603174591</v>
@@ -14221,7 +14222,7 @@
         <v>3.5977459904638027</v>
       </c>
       <c r="CR39" s="0">
-        <v>1.7577500798977292</v>
+        <v>1.7577500798977293</v>
       </c>
       <c r="CS39" s="0">
         <v>2.7937490785787973</v>
@@ -14490,7 +14491,7 @@
         <v>1.2164055534326828</v>
       </c>
       <c r="BM40" s="0">
-        <v>1.0545222782316463</v>
+        <v>1.0545222782316464</v>
       </c>
       <c r="BN40" s="0">
         <v>1.0555728034771801</v>
@@ -14526,7 +14527,7 @@
         <v>1.2480717991866488</v>
       </c>
       <c r="BY40" s="0">
-        <v>0.85005574136008843</v>
+        <v>0.85005574136008844</v>
       </c>
       <c r="BZ40" s="0">
         <v>1.2243285939968394</v>
@@ -14544,10 +14545,10 @@
         <v>1.1666666666666659</v>
       </c>
       <c r="CE40" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="CF40" s="0">
-        <v>1.4968336211859516</v>
+        <v>1.4968336211859517</v>
       </c>
       <c r="CG40" s="0">
         <v>1.0222773739880626</v>
@@ -14580,7 +14581,7 @@
         <v>0.92337210696726135</v>
       </c>
       <c r="CQ40" s="0">
-        <v>3.2997399219765899</v>
+        <v>3.29973992197659</v>
       </c>
       <c r="CR40" s="0">
         <v>1.2464046021092992</v>
@@ -14625,7 +14626,7 @@
         <v>0.72498791686805153</v>
       </c>
       <c r="DF40" s="0">
-        <v>1.6700749829584169</v>
+        <v>1.670074982958417</v>
       </c>
       <c r="DG40" s="0">
         <v>3.0487804878048754</v>
@@ -14663,7 +14664,7 @@
         <v>0.8694602101195501</v>
       </c>
       <c r="B41" s="0">
-        <v>0.76099682221107134</v>
+        <v>0.76099682221107135</v>
       </c>
       <c r="C41" s="0">
         <v>0.97805273236117163</v>
@@ -14693,7 +14694,7 @@
         <v>0.96921322690991929</v>
       </c>
       <c r="L41" s="0">
-        <v>1.1188066062866266</v>
+        <v>1.1188066062866267</v>
       </c>
       <c r="M41" s="0">
         <v>0.98406098406098319</v>
@@ -14768,7 +14769,7 @@
         <v>0.7843137254901954</v>
       </c>
       <c r="AK41" s="0">
-        <v>1.1440457618304722</v>
+        <v>1.1440457618304723</v>
       </c>
       <c r="AL41" s="0">
         <v>1.1801122073902097</v>
@@ -14777,7 +14778,7 @@
         <v>1.2974976830398506</v>
       </c>
       <c r="AN41" s="0">
-        <v>1.260321599304649</v>
+        <v>1.2603215993046491</v>
       </c>
       <c r="AO41" s="0">
         <v>1.1235955056179765</v>
@@ -14807,7 +14808,7 @@
         <v>1.1392177969142439</v>
       </c>
       <c r="AX41" s="0">
-        <v>1.4281373442722562</v>
+        <v>1.4281373442722563</v>
       </c>
       <c r="AY41" s="0">
         <v>1.1459386585776867</v>
@@ -14858,7 +14859,7 @@
         <v>1.1176653213287788</v>
       </c>
       <c r="BO41" s="0">
-        <v>1.2946076775863999</v>
+        <v>1.2946076775864</v>
       </c>
       <c r="BP41" s="0">
         <v>1.0067607289829503</v>
@@ -14876,10 +14877,10 @@
         <v>0.9751547528194684</v>
       </c>
       <c r="BU41" s="0">
-        <v>1.1397782613200695</v>
+        <v>1.1397782613200696</v>
       </c>
       <c r="BV41" s="0">
-        <v>1.2612612612612601</v>
+        <v>1.2612612612612602</v>
       </c>
       <c r="BW41" s="0">
         <v>1.5497076023391798</v>
@@ -14906,7 +14907,7 @@
         <v>1.217948717948717</v>
       </c>
       <c r="CE41" s="0">
-        <v>0.82539682539682468</v>
+        <v>0.82539682539682469</v>
       </c>
       <c r="CF41" s="0">
         <v>1.5544041450777188</v>
@@ -15139,7 +15140,7 @@
         <v>0.71053444547420397</v>
       </c>
       <c r="AN42" s="0">
-        <v>1.260321599304649</v>
+        <v>1.2603215993046491</v>
       </c>
       <c r="AO42" s="0">
         <v>0.95880149812734006</v>
@@ -15199,7 +15200,7 @@
         <v>1.0166358595194076</v>
       </c>
       <c r="BH42" s="0">
-        <v>0.82552431950022231</v>
+        <v>0.82552431950022232</v>
       </c>
       <c r="BI42" s="0">
         <v>0.90729783037475265</v>
@@ -15220,7 +15221,7 @@
         <v>1.2935941219083089</v>
       </c>
       <c r="BO42" s="0">
-        <v>1.3846673421141495</v>
+        <v>1.3846673421141496</v>
       </c>
       <c r="BP42" s="0">
         <v>0.97736625514403197</v>
@@ -15402,7 +15403,7 @@
         <v>1.1936529798284112</v>
       </c>
       <c r="G43" s="0">
-        <v>0.64102564102564052</v>
+        <v>0.64102564102564053</v>
       </c>
       <c r="H43" s="0">
         <v>0.77707134927843302</v>
@@ -15423,7 +15424,7 @@
         <v>0.80388080388080319</v>
       </c>
       <c r="N43" s="0">
-        <v>1.3084112149532698</v>
+        <v>1.3084112149532699</v>
       </c>
       <c r="O43" s="0">
         <v>0.83053193593039276</v>
@@ -15441,7 +15442,7 @@
         <v>0.78016160490387232</v>
       </c>
       <c r="T43" s="0">
-        <v>0.6282865533019184</v>
+        <v>0.62828655330191841</v>
       </c>
       <c r="U43" s="0">
         <v>1.1154489682097035</v>
@@ -15480,7 +15481,7 @@
         <v>1.2631578947368411</v>
       </c>
       <c r="AG43" s="0">
-        <v>0.7771238871284134</v>
+        <v>0.77712388712841341</v>
       </c>
       <c r="AH43" s="0">
         <v>1.3637805264827136</v>
@@ -15648,7 +15649,7 @@
         <v>1.2333965844402266</v>
       </c>
       <c r="CK43" s="0">
-        <v>0.66127430112104379</v>
+        <v>0.6612743011210438</v>
       </c>
       <c r="CL43" s="0">
         <v>0.96311734242768643</v>
@@ -15770,7 +15771,7 @@
         <v>0.66606115652437115</v>
       </c>
       <c r="I44" s="0">
-        <v>0.59246954595791756</v>
+        <v>0.59246954595791757</v>
       </c>
       <c r="J44" s="0">
         <v>0.65860988554255329</v>
@@ -15812,7 +15813,7 @@
         <v>1.3174019607843126</v>
       </c>
       <c r="W44" s="0">
-        <v>0.85470085470085388</v>
+        <v>0.85470085470085389</v>
       </c>
       <c r="X44" s="0">
         <v>1.1559598256585171</v>
@@ -15926,7 +15927,7 @@
         <v>0.54663096831771485</v>
       </c>
       <c r="BI44" s="0">
-        <v>0.79254079254079179</v>
+        <v>0.7925407925407918</v>
       </c>
       <c r="BJ44" s="0">
         <v>0.15109637000184251</v>
@@ -15992,7 +15993,7 @@
         <v>1.1666666666666659</v>
       </c>
       <c r="CE44" s="0">
-        <v>0.82539682539682468</v>
+        <v>0.82539682539682469</v>
       </c>
       <c r="CF44" s="0">
         <v>1.3241220495106494</v>
@@ -16046,7 +16047,7 @@
         <v>0</v>
       </c>
       <c r="CW44" s="0">
-        <v>0.4732435384055329</v>
+        <v>0.47324353840553291</v>
       </c>
       <c r="CX44" s="0">
         <v>0.30361137743688055</v>
@@ -16324,7 +16325,7 @@
         <v>0.73772576952429347</v>
       </c>
       <c r="BU45" s="0">
-        <v>1.1397782613200695</v>
+        <v>1.1397782613200696</v>
       </c>
       <c r="BV45" s="0">
         <v>0.80262080262080193</v>
@@ -16363,7 +16364,7 @@
         <v>0.61454824794658103</v>
       </c>
       <c r="CH45" s="0">
-        <v>0.62276401219027377</v>
+        <v>0.62276401219027378</v>
       </c>
       <c r="CI45" s="0">
         <v>1.1869107043815852</v>
@@ -16563,10 +16564,10 @@
         <v>1.0245901639344328</v>
       </c>
       <c r="AF46" s="0">
-        <v>1.5438596491228171</v>
+        <v>1.5438596491228172</v>
       </c>
       <c r="AG46" s="0">
-        <v>0.56586690810321782</v>
+        <v>0.56586690810321783</v>
       </c>
       <c r="AH46" s="0">
         <v>0.983190612115452</v>
@@ -16608,7 +16609,7 @@
         <v>1.1129660545353439</v>
       </c>
       <c r="AU46" s="0">
-        <v>0.45746785361028985</v>
+        <v>0.45746785361028986</v>
       </c>
       <c r="AV46" s="0">
         <v>1.1252701393546536</v>
@@ -16635,7 +16636,7 @@
         <v>1.244286439817174</v>
       </c>
       <c r="BD46" s="0">
-        <v>0.77423775265502381</v>
+        <v>0.77423775265502382</v>
       </c>
       <c r="BE46" s="0">
         <v>0.25003906860447112</v>
@@ -16653,7 +16654,7 @@
         <v>0.69212838443608127</v>
       </c>
       <c r="BJ46" s="0">
-        <v>0.12529942878201666</v>
+        <v>0.12529942878201667</v>
       </c>
       <c r="BK46" s="0">
         <v>0.68686036128855454</v>
@@ -16665,7 +16666,7 @@
         <v>0.61996639434498346</v>
       </c>
       <c r="BN46" s="0">
-        <v>1.1590603332298532</v>
+        <v>1.1590603332298533</v>
       </c>
       <c r="BO46" s="0">
         <v>1.0019137678712211</v>
@@ -16695,7 +16696,7 @@
         <v>1.14035087719299</v>
       </c>
       <c r="BX46" s="0">
-        <v>0.40667508063385482</v>
+        <v>0.40667508063385483</v>
       </c>
       <c r="BY46" s="0">
         <v>0.45986622073578892</v>
@@ -16832,7 +16833,7 @@
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>0.5031598438191841</v>
+        <v>0.50315984381918411</v>
       </c>
       <c r="B47" s="0">
         <v>0.37213580866365581</v>
@@ -16868,7 +16869,7 @@
         <v>0.69259456579648304</v>
       </c>
       <c r="M47" s="0">
-        <v>0.44352044352044317</v>
+        <v>0.44352044352044318</v>
       </c>
       <c r="N47" s="0">
         <v>0.92419522326064307</v>
@@ -16892,13 +16893,13 @@
         <v>0.36877688998156083</v>
       </c>
       <c r="U47" s="0">
-        <v>1.0968581520728748</v>
+        <v>1.0968581520728749</v>
       </c>
       <c r="V47" s="0">
         <v>1.0723039215686263</v>
       </c>
       <c r="W47" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="X47" s="0">
         <v>1.0612090202766715</v>
@@ -16976,7 +16977,7 @@
         <v>1.1178180192264691</v>
       </c>
       <c r="AW47" s="0">
-        <v>0.60100466451381362</v>
+        <v>0.60100466451381363</v>
       </c>
       <c r="AX47" s="0">
         <v>0.84067659272764028</v>
@@ -17012,7 +17013,7 @@
         <v>0.45180722891566227</v>
       </c>
       <c r="BI47" s="0">
-        <v>0.65626681011296339</v>
+        <v>0.6562668101129634</v>
       </c>
       <c r="BJ47" s="0">
         <v>0.12529942878201575</v>
@@ -17072,7 +17073,7 @@
         <v>0.73490813648293896</v>
       </c>
       <c r="CC47" s="0">
-        <v>0.32495938007749003</v>
+        <v>0.32495938007749004</v>
       </c>
       <c r="CD47" s="0">
         <v>1.0512820512820502</v>
@@ -17087,7 +17088,7 @@
         <v>0.4904567748035214</v>
       </c>
       <c r="CH47" s="0">
-        <v>0.43284307230245977</v>
+        <v>0.43284307230245978</v>
       </c>
       <c r="CI47" s="0">
         <v>0.94287298946200693</v>
@@ -17239,7 +17240,7 @@
         <v>0.40208292136312668</v>
       </c>
       <c r="P48" s="0">
-        <v>0.29574020360575531</v>
+        <v>0.29574020360575532</v>
       </c>
       <c r="Q48" s="0">
         <v>0.61728395061728336</v>
@@ -17293,7 +17294,7 @@
         <v>0.40742417383431379</v>
       </c>
       <c r="AH48" s="0">
-        <v>0.9118300031715818</v>
+        <v>0.91183000317158181</v>
       </c>
       <c r="AI48" s="0">
         <v>0.99320968886186189</v>
@@ -17371,7 +17372,7 @@
         <v>0.69624152803450334</v>
       </c>
       <c r="BH48" s="0">
-        <v>0.44065149486836191</v>
+        <v>0.44065149486836192</v>
       </c>
       <c r="BI48" s="0">
         <v>0.49847588309126728</v>
@@ -17422,7 +17423,7 @@
         <v>0.51886130977422473</v>
       </c>
       <c r="BY48" s="0">
-        <v>0.34838350055741329</v>
+        <v>0.3483835005574133</v>
       </c>
       <c r="BZ48" s="0">
         <v>0.77672459189046794</v>
@@ -17682,7 +17683,7 @@
         <v>0.5150846210448855</v>
       </c>
       <c r="AQ49" s="0">
-        <v>0.55793991416308963</v>
+        <v>0.55793991416308964</v>
       </c>
       <c r="AR49" s="0">
         <v>0.95950155763239797</v>
@@ -17694,10 +17695,10 @@
         <v>0.83472454090150183</v>
       </c>
       <c r="AU49" s="0">
-        <v>0.24109792284866446</v>
+        <v>0.24109792284866447</v>
       </c>
       <c r="AV49" s="0">
-        <v>1.0507489380728809</v>
+        <v>1.050748938072881</v>
       </c>
       <c r="AW49" s="0">
         <v>0.67276641550053762</v>
@@ -17733,7 +17734,7 @@
         <v>0.69624152803450334</v>
       </c>
       <c r="BH49" s="0">
-        <v>0.32909415439535888</v>
+        <v>0.32909415439535889</v>
       </c>
       <c r="BI49" s="0">
         <v>0.44109736417428685</v>
@@ -17927,7 +17928,7 @@
         <v>0.36824274561791098</v>
       </c>
       <c r="D50" s="0">
-        <v>0.50542305275523824</v>
+        <v>0.50542305275523825</v>
       </c>
       <c r="E50" s="0">
         <v>0.52020060430489312</v>
@@ -17942,7 +17943,7 @@
         <v>0.41376526390150331</v>
       </c>
       <c r="I50" s="0">
-        <v>0.24916943521594664</v>
+        <v>0.24916943521594665</v>
       </c>
       <c r="J50" s="0">
         <v>0.25577082933691386</v>
@@ -17975,7 +17976,7 @@
         <v>0.33899879260703975</v>
       </c>
       <c r="T50" s="0">
-        <v>0.21853445332240642</v>
+        <v>0.21853445332240643</v>
       </c>
       <c r="U50" s="0">
         <v>0.89235917456776281</v>
@@ -17987,7 +17988,7 @@
         <v>1.2136752136752125</v>
       </c>
       <c r="X50" s="0">
-        <v>0.73905628197839623</v>
+        <v>0.73905628197839624</v>
       </c>
       <c r="Y50" s="0">
         <v>0.49790356394129937</v>
@@ -18140,7 +18141,7 @@
         <v>0.62244062244062193</v>
       </c>
       <c r="BW50" s="0">
-        <v>0.80409356725146119</v>
+        <v>0.8040935672514612</v>
       </c>
       <c r="BX50" s="0">
         <v>0.22437245828074584</v>
@@ -18340,7 +18341,7 @@
         <v>0.17073004165813002</v>
       </c>
       <c r="U51" s="0">
-        <v>0.76222346160996401</v>
+        <v>0.76222346160996402</v>
       </c>
       <c r="V51" s="0">
         <v>0.93443627450980316</v>
@@ -18349,7 +18350,7 @@
         <v>1.2991452991452981</v>
       </c>
       <c r="X51" s="0">
-        <v>0.83380708736024189</v>
+        <v>0.8338070873602419</v>
       </c>
       <c r="Y51" s="0">
         <v>0.36687631027253637</v>
@@ -18382,7 +18383,7 @@
         <v>0.6739613066920388</v>
       </c>
       <c r="AI51" s="0">
-        <v>0.83105300496604761</v>
+        <v>0.83105300496604762</v>
       </c>
       <c r="AJ51" s="0">
         <v>0.19607843137254885</v>
@@ -18415,7 +18416,7 @@
         <v>0.99206349206349109</v>
       </c>
       <c r="AT51" s="0">
-        <v>0.44518642181413431</v>
+        <v>0.44518642181413432</v>
       </c>
       <c r="AU51" s="0">
         <v>0.12982195845697317</v>
@@ -18424,7 +18425,7 @@
         <v>0.98367985691929272</v>
       </c>
       <c r="AW51" s="0">
-        <v>0.52027269465374903</v>
+        <v>0.52027269465374904</v>
       </c>
       <c r="AX51" s="0">
         <v>0.44565988048212257</v>
@@ -18436,7 +18437,7 @@
         <v>0.54341113992836809</v>
       </c>
       <c r="BA51" s="0">
-        <v>0.220195029883611</v>
+        <v>0.22019502988361101</v>
       </c>
       <c r="BB51" s="0">
         <v>0.54208555095604127</v>
@@ -18523,7 +18524,7 @@
         <v>0.087489063867016548</v>
       </c>
       <c r="CD51" s="0">
-        <v>0.8846153846153838</v>
+        <v>0.88461538461538381</v>
       </c>
       <c r="CE51" s="0">
         <v>0.44444444444444409</v>
@@ -18556,7 +18557,7 @@
         <v>0.99306054079923334</v>
       </c>
       <c r="CO51" s="0">
-        <v>0.13224014810896575</v>
+        <v>0.13224014810896576</v>
       </c>
       <c r="CP51" s="0">
         <v>0.27581244753567552</v>
@@ -18645,7 +18646,7 @@
         <v>0.24956728253431526</v>
       </c>
       <c r="B52" s="0">
-        <v>0.17561465127947803</v>
+        <v>0.17561465127947804</v>
       </c>
       <c r="C52" s="0">
         <v>0.26513477684489589</v>
@@ -18702,7 +18703,7 @@
         <v>0.12975483166017882</v>
       </c>
       <c r="U52" s="0">
-        <v>0.76222346160996401</v>
+        <v>0.76222346160996402</v>
       </c>
       <c r="V52" s="0">
         <v>0.6587009803921563</v>
@@ -18789,7 +18790,7 @@
         <v>0.36777897380696056</v>
       </c>
       <c r="AX52" s="0">
-        <v>0.31398764306694998</v>
+        <v>0.31398764306694999</v>
       </c>
       <c r="AY52" s="0">
         <v>0.89652847994607265</v>
@@ -18828,7 +18829,7 @@
         <v>0.033167495854062985</v>
       </c>
       <c r="BK52" s="0">
-        <v>0.37777319870870218</v>
+        <v>0.37777319870870219</v>
       </c>
       <c r="BL52" s="0">
         <v>0.49038339065087205</v>
@@ -18864,7 +18865,7 @@
         <v>0.34398034398034366</v>
       </c>
       <c r="BW52" s="0">
-        <v>0.73099415204678297</v>
+        <v>0.73099415204678298</v>
       </c>
       <c r="BX52" s="0">
         <v>0.22437245828074584</v>
@@ -19061,7 +19062,7 @@
         <v>0.19039658214915928</v>
       </c>
       <c r="T53" s="0">
-        <v>0.18438844499078041</v>
+        <v>0.18438844499078042</v>
       </c>
       <c r="U53" s="0">
         <v>0.48336121955753814</v>
@@ -19091,7 +19092,7 @@
         <v>0.56737588652482218</v>
       </c>
       <c r="AD53" s="0">
-        <v>1.4513442778967391</v>
+        <v>1.4513442778967392</v>
       </c>
       <c r="AE53" s="0">
         <v>0.40983606557377011</v>
@@ -19103,7 +19104,7 @@
         <v>0.15089784216085697</v>
       </c>
       <c r="AH53" s="0">
-        <v>0.5470980019029491</v>
+        <v>0.54709800190294911</v>
       </c>
       <c r="AI53" s="0">
         <v>0.72970507753116387</v>
@@ -19139,7 +19140,7 @@
         <v>1.3888888888888875</v>
       </c>
       <c r="AT53" s="0">
-        <v>0.44518642181413431</v>
+        <v>0.44518642181413432</v>
       </c>
       <c r="AU53" s="0">
         <v>0.11745796241345191</v>
@@ -19151,7 +19152,7 @@
         <v>0.24219590958019352</v>
       </c>
       <c r="AX53" s="0">
-        <v>0.41527397954015965</v>
+        <v>0.41527397954015966</v>
       </c>
       <c r="AY53" s="0">
         <v>0.77519379844961167</v>
@@ -19513,10 +19514,10 @@
         <v>0.21528525296017204</v>
       </c>
       <c r="AX54" s="0">
-        <v>0.37475944495087576</v>
+        <v>0.37475944495087577</v>
       </c>
       <c r="AY54" s="0">
-        <v>0.71452645770138123</v>
+        <v>0.71452645770138124</v>
       </c>
       <c r="AZ54" s="0">
         <v>0.50636038038779752</v>
@@ -19534,7 +19535,7 @@
         <v>0.21240150736553595</v>
       </c>
       <c r="BE54" s="0">
-        <v>0.031254883575558653</v>
+        <v>0.031254883575558654</v>
       </c>
       <c r="BF54" s="0">
         <v>0.33319450229071196</v>
@@ -19606,7 +19607,7 @@
         <v>0.2099737532808397</v>
       </c>
       <c r="CC54" s="0">
-        <v>0.074990626171728469</v>
+        <v>0.07499062617172847</v>
       </c>
       <c r="CD54" s="0">
         <v>0.5897435897435892</v>
@@ -19645,7 +19646,7 @@
         <v>0.07493608392841393</v>
       </c>
       <c r="CP54" s="0">
-        <v>0.12791301914697994</v>
+        <v>0.12791301914697995</v>
       </c>
       <c r="CQ54" s="0">
         <v>0</v>
@@ -19743,10 +19744,10 @@
         <v>0.19624334174376357</v>
       </c>
       <c r="F55" s="0">
-        <v>0.34432297495050584</v>
+        <v>0.34432297495050585</v>
       </c>
       <c r="G55" s="0">
-        <v>0.1335470085470094</v>
+        <v>0.13354700854700941</v>
       </c>
       <c r="H55" s="0">
         <v>0.23211222121304018</v>
@@ -19785,7 +19786,7 @@
         <v>0.15788984861149913</v>
       </c>
       <c r="T55" s="0">
-        <v>0.081950419995903009</v>
+        <v>0.08195041999590301</v>
       </c>
       <c r="U55" s="0">
         <v>0.353225506599742</v>
@@ -19809,7 +19810,7 @@
         <v>0.46907065376722679</v>
       </c>
       <c r="AB55" s="0">
-        <v>0.34743511138361149</v>
+        <v>0.3474351113836115</v>
       </c>
       <c r="AC55" s="0">
         <v>0.37825059101655095</v>
@@ -19824,7 +19825,7 @@
         <v>0.56140350877193346</v>
       </c>
       <c r="AG55" s="0">
-        <v>0.090538705296514851</v>
+        <v>0.090538705296514852</v>
       </c>
       <c r="AH55" s="0">
         <v>0.57088487155090761</v>
@@ -19935,7 +19936,7 @@
         <v>0.083752093802345606</v>
       </c>
       <c r="BR55" s="0">
-        <v>0.19375151368370191</v>
+        <v>0.19375151368370192</v>
       </c>
       <c r="BS55" s="0">
         <v>0.060584030049679299</v>
@@ -20201,7 +20202,7 @@
         <v>0.15600624024960985</v>
       </c>
       <c r="AL56" s="0">
-        <v>0.22570452053911116</v>
+        <v>0.22570452053911117</v>
       </c>
       <c r="AM56" s="0">
         <v>0.092678405931417893</v>
@@ -20249,10 +20250,10 @@
         <v>0.062912865681031716</v>
       </c>
       <c r="BB56" s="0">
-        <v>0.24640252316183694</v>
+        <v>0.24640252316183695</v>
       </c>
       <c r="BC56" s="0">
-        <v>0.51633654985610244</v>
+        <v>0.51633654985610245</v>
       </c>
       <c r="BD56" s="0">
         <v>0.21925316889345647</v>
@@ -20303,7 +20304,7 @@
         <v>0.084817642069550392</v>
       </c>
       <c r="BT56" s="0">
-        <v>0.12295429492071556</v>
+        <v>0.12295429492071557</v>
       </c>
       <c r="BU56" s="0">
         <v>0.58025075121748992</v>
@@ -20617,7 +20618,7 @@
         <v>0.40206534619942402</v>
       </c>
       <c r="BD57" s="0">
-        <v>0.13018156903048977</v>
+        <v>0.13018156903048978</v>
       </c>
       <c r="BE57" s="0">
         <v>0.04688232536333798</v>
@@ -20644,7 +20645,7 @@
         <v>0.28021908037192689</v>
       </c>
       <c r="BM57" s="0">
-        <v>0.092705255229155722</v>
+        <v>0.092705255229155723</v>
       </c>
       <c r="BN57" s="0">
         <v>0.58987891959018879</v>
@@ -20710,7 +20711,7 @@
         <v>0.088335320878053</v>
       </c>
       <c r="CI57" s="0">
-        <v>0.44370493621741502</v>
+        <v>0.44370493621741503</v>
       </c>
       <c r="CJ57" s="0">
         <v>0.33733923676997651</v>
@@ -20895,7 +20896,7 @@
         <v>0.11726766344180582</v>
       </c>
       <c r="AB58" s="0">
-        <v>0.20437359493153467</v>
+        <v>0.20437359493153468</v>
       </c>
       <c r="AC58" s="0">
         <v>0.23640661938534258</v>
@@ -20943,7 +20944,7 @@
         <v>0.100143061516452</v>
       </c>
       <c r="AR58" s="0">
-        <v>0.41121495327102769</v>
+        <v>0.4112149532710277</v>
       </c>
       <c r="AS58" s="0">
         <v>0.79365079365079294</v>
@@ -20952,7 +20953,7 @@
         <v>0.33388981636060072</v>
       </c>
       <c r="AU58" s="0">
-        <v>0.037091988130563767</v>
+        <v>0.037091988130563768</v>
       </c>
       <c r="AV58" s="0">
         <v>0.44712720769058761</v>
@@ -21006,7 +21007,7 @@
         <v>0.1464781556489618</v>
       </c>
       <c r="BM58" s="0">
-        <v>0.092705255229155722</v>
+        <v>0.092705255229155723</v>
       </c>
       <c r="BN58" s="0">
         <v>0.61057642554072189</v>
@@ -21054,7 +21055,7 @@
         <v>0.5774278215223092</v>
       </c>
       <c r="CC58" s="0">
-        <v>0.024996875390576156</v>
+        <v>0.024996875390576157</v>
       </c>
       <c r="CD58" s="0">
         <v>0.2948717948717946</v>
@@ -21072,7 +21073,7 @@
         <v>0.035334128351221204</v>
       </c>
       <c r="CI58" s="0">
-        <v>0.62118691070438103</v>
+        <v>0.62118691070438104</v>
       </c>
       <c r="CJ58" s="0">
         <v>0.28462998102466769</v>
@@ -21338,7 +21339,7 @@
         <v>0.11827321111768174</v>
       </c>
       <c r="BC59" s="0">
-        <v>0.36397494498053123</v>
+        <v>0.36397494498053124</v>
       </c>
       <c r="BD59" s="0">
         <v>0.068516615279205148</v>
@@ -21365,7 +21366,7 @@
         <v>0.061817432515969446</v>
       </c>
       <c r="BL59" s="0">
-        <v>0.16558400203795678</v>
+        <v>0.16558400203795679</v>
       </c>
       <c r="BM59" s="0">
         <v>0.057940784518222328</v>
@@ -21413,7 +21414,7 @@
         <v>0.45112781954887177</v>
       </c>
       <c r="CB59" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC59" s="0">
         <v>0.012498437695288078</v>
@@ -21574,7 +21575,7 @@
         <v>0.071035340081690573</v>
       </c>
       <c r="M60" s="0">
-        <v>0.027720027720027698</v>
+        <v>0.027720027720027699</v>
       </c>
       <c r="N60" s="0">
         <v>0.10384215991692618</v>
@@ -21640,7 +21641,7 @@
         <v>0.23786869647954309</v>
       </c>
       <c r="AI60" s="0">
-        <v>0.21283064761325612</v>
+        <v>0.21283064761325613</v>
       </c>
       <c r="AJ60" s="0">
         <v>0.051599587203302329</v>
@@ -21655,10 +21656,10 @@
         <v>0.1235712079085572</v>
       </c>
       <c r="AN60" s="0">
-        <v>0.21729682746631881</v>
+        <v>0.21729682746631882</v>
       </c>
       <c r="AO60" s="0">
-        <v>0.089887640449438116</v>
+        <v>0.089887640449438117</v>
       </c>
       <c r="AP60" s="0">
         <v>0.073583517292126505</v>
@@ -21775,7 +21776,7 @@
         <v>0.40100250626566381</v>
       </c>
       <c r="CB60" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC60" s="0">
         <v>0.012498437695288078</v>
@@ -21802,7 +21803,7 @@
         <v>0.27408812987560593</v>
       </c>
       <c r="CK60" s="0">
-        <v>0.017028522775649198</v>
+        <v>0.017028522775649199</v>
       </c>
       <c r="CL60" s="0">
         <v>0.085259568018188625</v>
@@ -21936,7 +21937,7 @@
         <v>0.035517670040845287</v>
       </c>
       <c r="M61" s="0">
-        <v>0.027720027720027698</v>
+        <v>0.027720027720027699</v>
       </c>
       <c r="N61" s="0">
         <v>0.1142263759086188</v>
@@ -22020,7 +22021,7 @@
         <v>0.26075619295958258</v>
       </c>
       <c r="AO61" s="0">
-        <v>0.089887640449438116</v>
+        <v>0.089887640449438117</v>
       </c>
       <c r="AP61" s="0">
         <v>0.058866813833701195</v>
@@ -22113,7 +22114,7 @@
         <v>0.01211680600993577</v>
       </c>
       <c r="BT61" s="0">
-        <v>0.072076655643178097</v>
+        <v>0.072076655643178098</v>
       </c>
       <c r="BU61" s="0">
         <v>0.38337996062584156</v>
@@ -22134,13 +22135,13 @@
         <v>0.06582411795681932</v>
       </c>
       <c r="CA61" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB61" s="0">
         <v>0.10498687664041985</v>
       </c>
       <c r="CC61" s="0">
-        <v>0.024996875390576156</v>
+        <v>0.024996875390576157</v>
       </c>
       <c r="CD61" s="0">
         <v>0.15384615384615372</v>
@@ -22379,7 +22380,7 @@
         <v>0.030892801977139301</v>
       </c>
       <c r="AN62" s="0">
-        <v>0.17383746197305502</v>
+        <v>0.17383746197305503</v>
       </c>
       <c r="AO62" s="0">
         <v>0.059925093632958754</v>
@@ -22427,7 +22428,7 @@
         <v>0.22007787370915841</v>
       </c>
       <c r="BD62" s="0">
-        <v>0.054813292223364118</v>
+        <v>0.054813292223364119</v>
       </c>
       <c r="BE62" s="0">
         <v>0</v>
@@ -22502,7 +22503,7 @@
         <v>0.10498687664041985</v>
       </c>
       <c r="CC62" s="0">
-        <v>0.024996875390576156</v>
+        <v>0.024996875390576157</v>
       </c>
       <c r="CD62" s="0">
         <v>0.16666666666666652</v>
@@ -22529,7 +22530,7 @@
         <v>0.019866609904924067</v>
       </c>
       <c r="CL62" s="0">
-        <v>0.047366426676771461</v>
+        <v>0.047366426676771462</v>
       </c>
       <c r="CM62" s="0">
         <v>0.35401527855412673</v>
@@ -22669,7 +22670,7 @@
         <v>0.0065915233010349124</v>
       </c>
       <c r="P63" s="0">
-        <v>0.0056873116078030288</v>
+        <v>0.0056873116078030289</v>
       </c>
       <c r="Q63" s="0">
         <v>0</v>
@@ -22693,7 +22694,7 @@
         <v>0.73504273504273976</v>
       </c>
       <c r="X63" s="0">
-        <v>0.075800644305477088</v>
+        <v>0.075800644305477089</v>
       </c>
       <c r="Y63" s="0">
         <v>0</v>
@@ -22834,7 +22835,7 @@
         <v>0.016145959473641825</v>
       </c>
       <c r="BS63" s="0">
-        <v>0.0040389353366452867</v>
+        <v>0.0040389353366452868</v>
       </c>
       <c r="BT63" s="0">
         <v>0.033918426185025233</v>
@@ -22882,7 +22883,7 @@
         <v>0.017667064175610731</v>
       </c>
       <c r="CI63" s="0">
-        <v>0.17748197448696731</v>
+        <v>0.17748197448696732</v>
       </c>
       <c r="CJ63" s="0">
         <v>0.13704406493780397</v>
@@ -23151,7 +23152,7 @@
         <v>0.13966480446927362</v>
       </c>
       <c r="BD64" s="0">
-        <v>0.020554984583761544</v>
+        <v>0.020554984583761545</v>
       </c>
       <c r="BE64" s="0">
         <v>0</v>
@@ -23193,7 +23194,7 @@
         <v>0.011964584828906426</v>
       </c>
       <c r="BR64" s="0">
-        <v>0.024218939210462562</v>
+        <v>0.024218939210462563</v>
       </c>
       <c r="BS64" s="0">
         <v>0.0040389353366452564</v>
@@ -23561,7 +23562,7 @@
         <v>0</v>
       </c>
       <c r="BT65" s="0">
-        <v>0.0084796065462562457</v>
+        <v>0.0084796065462562458</v>
       </c>
       <c r="BU65" s="0">
         <v>0.19687079059164836</v>
@@ -23746,10 +23747,10 @@
         <v>0.017758835020422643</v>
       </c>
       <c r="M66" s="0">
-        <v>0.027720027720027698</v>
+        <v>0.027720027720027699</v>
       </c>
       <c r="N66" s="0">
-        <v>0.041536863966770476</v>
+        <v>0.041536863966770477</v>
       </c>
       <c r="O66" s="0">
         <v>0</v>
@@ -23875,7 +23876,7 @@
         <v>0.088877602844083206</v>
       </c>
       <c r="BD66" s="0">
-        <v>0.020554984583761544</v>
+        <v>0.020554984583761545</v>
       </c>
       <c r="BE66" s="0">
         <v>0</v>
@@ -23926,7 +23927,7 @@
         <v>0.0042398032731281229</v>
       </c>
       <c r="BU66" s="0">
-        <v>0.15542430836182763</v>
+        <v>0.15542430836182764</v>
       </c>
       <c r="BV66" s="0">
         <v>0.049140049140049095</v>
@@ -23971,7 +23972,7 @@
         <v>0.17748197448696601</v>
       </c>
       <c r="CJ66" s="0">
-        <v>0.031625553447185296</v>
+        <v>0.031625553447185297</v>
       </c>
       <c r="CK66" s="0">
         <v>0.0056761742585497328</v>
@@ -24117,7 +24118,7 @@
         <v>0</v>
       </c>
       <c r="P67" s="0">
-        <v>0.0056873116078030288</v>
+        <v>0.0056873116078030289</v>
       </c>
       <c r="Q67" s="0">
         <v>0.051440329218107331</v>
@@ -24141,7 +24142,7 @@
         <v>0.23931623931624088</v>
       </c>
       <c r="X67" s="0">
-        <v>0.075800644305477088</v>
+        <v>0.075800644305477089</v>
       </c>
       <c r="Y67" s="0">
         <v>0</v>
@@ -24267,7 +24268,7 @@
         <v>0.011588156903644552</v>
       </c>
       <c r="BN67" s="0">
-        <v>0.15523129462899823</v>
+        <v>0.15523129462899824</v>
       </c>
       <c r="BO67" s="0">
         <v>0.011257458065968779</v>
@@ -24288,7 +24289,7 @@
         <v>0</v>
       </c>
       <c r="BU67" s="0">
-        <v>0.082892964459642018</v>
+        <v>0.082892964459642019</v>
       </c>
       <c r="BV67" s="0">
         <v>0.032760032760032975</v>
@@ -24315,7 +24316,7 @@
         <v>0</v>
       </c>
       <c r="CD67" s="0">
-        <v>0.038461538461538713</v>
+        <v>0.038461538461538714</v>
       </c>
       <c r="CE67" s="0">
         <v>0</v>
@@ -24333,7 +24334,7 @@
         <v>0.12201885745979003</v>
       </c>
       <c r="CJ67" s="0">
-        <v>0.042167404596247376</v>
+        <v>0.042167404596247377</v>
       </c>
       <c r="CK67" s="0">
         <v>0</v>
@@ -24449,7 +24450,7 @@
         <v>0.0093449210354171735</v>
       </c>
       <c r="F68" s="0">
-        <v>0.017216148747525035</v>
+        <v>0.017216148747525036</v>
       </c>
       <c r="G68" s="0">
         <v>0</v>
@@ -24467,7 +24468,7 @@
         <v>0</v>
       </c>
       <c r="L68" s="0">
-        <v>0.017758835020422511</v>
+        <v>0.017758835020422512</v>
       </c>
       <c r="M68" s="0">
         <v>0</v>
@@ -25257,7 +25258,7 @@
         <v>0</v>
       </c>
       <c r="AH70" s="0">
-        <v>0.023786869647954133</v>
+        <v>0.023786869647954134</v>
       </c>
       <c r="AI70" s="0">
         <v>0.020269585486976622</v>
@@ -25425,10 +25426,10 @@
         <v>0</v>
       </c>
       <c r="CL70" s="0">
-        <v>0.0094732853353542232</v>
+        <v>0.0094732853353542233</v>
       </c>
       <c r="CM70" s="0">
-        <v>0.074529532327184025</v>
+        <v>0.074529532327184026</v>
       </c>
       <c r="CN70" s="0">
         <v>0.023929169657812676</v>
@@ -26137,7 +26138,7 @@
         <v>0.011818235537434163</v>
       </c>
       <c r="CH72" s="0">
-        <v>0.0088335320878052351</v>
+        <v>0.0088335320878052352</v>
       </c>
       <c r="CI72" s="0">
         <v>0.022185246810870588</v>
@@ -26705,7 +26706,7 @@
         <v>0</v>
       </c>
       <c r="AH74" s="0">
-        <v>0.023786869647954133</v>
+        <v>0.023786869647954134</v>
       </c>
       <c r="AI74" s="0">
         <v>0.010134792743488311</v>
@@ -26804,7 +26805,7 @@
         <v>0.020697505950532789</v>
       </c>
       <c r="BO74" s="0">
-        <v>0.022514916131937224</v>
+        <v>0.022514916131937225</v>
       </c>
       <c r="BP74" s="0">
         <v>0</v>
@@ -27055,7 +27056,7 @@
         <v>0</v>
       </c>
       <c r="AD75" s="0">
-        <v>0.023792529145848357</v>
+        <v>0.023792529145848358</v>
       </c>
       <c r="AE75" s="0">
         <v>0</v>
@@ -27178,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="BS75" s="0">
-        <v>0.0040389353366452867</v>
+        <v>0.0040389353366452868</v>
       </c>
       <c r="BT75" s="0">
         <v>0</v>
@@ -27725,7 +27726,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="0">
-        <v>0.017758835020422511</v>
+        <v>0.017758835020422512</v>
       </c>
       <c r="M77" s="0">
         <v>0</v>
@@ -27758,7 +27759,7 @@
         <v>0.03063725490196053</v>
       </c>
       <c r="W77" s="0">
-        <v>0.017094017094016953</v>
+        <v>0.017094017094016954</v>
       </c>
       <c r="X77" s="0">
         <v>0.018950161076368991</v>
@@ -28141,7 +28142,7 @@
         <v>0</v>
       </c>
       <c r="AD78" s="0">
-        <v>0.023792529145848357</v>
+        <v>0.023792529145848358</v>
       </c>
       <c r="AE78" s="0">
         <v>0</v>
@@ -29206,7 +29207,7 @@
         <v>0.015318627450980265</v>
       </c>
       <c r="W81" s="0">
-        <v>0.017094017094016953</v>
+        <v>0.017094017094016954</v>
       </c>
       <c r="X81" s="0">
         <v>0</v>
@@ -30313,7 +30314,7 @@
         <v>0</v>
       </c>
       <c r="AD84" s="0">
-        <v>0.023792529145848357</v>
+        <v>0.023792529145848358</v>
       </c>
       <c r="AE84" s="0">
         <v>0</v>

--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0003_ses-01_pet_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0003_ses-01_pet_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
